--- a/excel_automation/students.xlsx
+++ b/excel_automation/students.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f25aa4a93b616c7/Documents/git_assignment/excel_automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E63D24-A7F3-4E31-8178-4D2B9ABFCDD7}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Name</t>
   </si>
@@ -28,29 +28,50 @@
     <t>Marks</t>
   </si>
   <si>
-    <t>Nikhitha</t>
-  </si>
-  <si>
     <t>Rahul</t>
   </si>
   <si>
     <t>Priya</t>
   </si>
   <si>
-    <t>Kiran</t>
-  </si>
-  <si>
-    <t>Anu</t>
-  </si>
-  <si>
-    <t>AGE</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -59,6 +80,11 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -87,10 +113,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -304,7 +336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -312,69 +344,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="26" spans="10:13" ht="13.9">
+      <c r="J26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="10:13">
+      <c r="J27" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="M27" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="10:13">
+      <c r="J28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>90</v>
-      </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="K28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L28" s="3">
+        <v>85</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="10:13">
+      <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>85</v>
-      </c>
-      <c r="C3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>95</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>78</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>88</v>
-      </c>
-      <c r="C6">
-        <v>19</v>
+      <c r="K29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="3">
+        <v>72</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="10:13">
+      <c r="J30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="3">
+        <v>91</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="10:13">
+      <c r="J31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" s="3">
+        <v>48</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/excel_automation/students.xlsx
+++ b/excel_automation/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f25aa4a93b616c7/Documents/git_assignment/excel_automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E63D24-A7F3-4E31-8178-4D2B9ABFCDD7}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF4B08B-DCAC-4DD2-86C9-4ED1A9889101}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,6 +141,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -343,94 +347,132 @@
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.9">
+    <row r="1" spans="1:5" ht="13.9">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
+    <row r="3" spans="1:5" ht="13.9">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>85</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3">
+        <v>72</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>91</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="10:13">
+      <c r="J25" s="3"/>
+    </row>
     <row r="26" spans="10:13" ht="13.9">
-      <c r="J26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
     </row>
     <row r="27" spans="10:13">
-      <c r="J27" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
     </row>
     <row r="28" spans="10:13">
-      <c r="J28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L28" s="3">
-        <v>85</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
     </row>
     <row r="29" spans="10:13">
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L29" s="3">
-        <v>72</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
     </row>
     <row r="30" spans="10:13">
-      <c r="J30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L30" s="3">
-        <v>91</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
     </row>
     <row r="31" spans="10:13">
-      <c r="J31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L31" s="3">
-        <v>48</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_automation/students.xlsx
+++ b/excel_automation/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f25aa4a93b616c7/Documents/git_assignment/excel_automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF4B08B-DCAC-4DD2-86C9-4ED1A9889101}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{37E605C9-5682-4E11-BBCD-446283259973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ACA9168-A4B1-431E-BF10-AB37E91ED8F8}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Sneha</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -347,92 +347,92 @@
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.9">
+    <row r="1" spans="1:4" ht="13.9">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="13.9">
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="1:4" ht="13.9">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="3">
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3">
-        <v>85</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="3">
+        <v>72</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3">
-        <v>72</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C6" s="3">
+        <v>91</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3">
-        <v>91</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C7" s="3">
         <v>48</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
